--- a/exports/PAGEIND_full_report.xlsx
+++ b/exports/PAGEIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.29</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>42925.55</v>
+        <v>42600</v>
       </c>
       <c r="I2" t="n">
         <v>42759.04878089029</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.7</v>
+        <v>-2.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.99</v>
+        <v>3.22</v>
       </c>
       <c r="M2" t="n">
         <v>0.82</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.04</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>42510</v>
+        <v>43300</v>
       </c>
       <c r="I3" t="n">
         <v>43220.07668122638</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0.21</v>
+        <v>-1.64</v>
       </c>
       <c r="L3" t="n">
         <v>3.76</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.59</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44602.55208333334</v>
+        <v>44603.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>40989</v>
+        <v>40340.55</v>
       </c>
       <c r="I4" t="n">
         <v>40372.90077945362</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.34</v>
+        <v>-6.83</v>
       </c>
       <c r="L4" t="n">
         <v>6.9</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>8.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44608.55208333334</v>
+        <v>44609.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>41200</v>
+        <v>42929.45</v>
       </c>
       <c r="I5" t="n">
         <v>42086.92631968007</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.13</v>
+        <v>-6.42</v>
       </c>
       <c r="L5" t="n">
-        <v>3.25</v>
+        <v>6.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="N5" t="n">
         <v>5.88</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44628.38541666666</v>
+        <v>44628.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>39566</v>
+        <v>39406</v>
       </c>
       <c r="I6" t="n">
         <v>39548.2977438679</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.83</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>8.220000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>3.22</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.89</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>42120</v>
+        <v>42722.85</v>
       </c>
       <c r="I7" t="n">
         <v>42122.94047669131</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.89</v>
+        <v>-8.42</v>
       </c>
       <c r="L7" t="n">
-        <v>7.85</v>
+        <v>9.32</v>
       </c>
       <c r="M7" t="n">
         <v>2.22</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44648.38541666666</v>
+        <v>44648.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>40366.3</v>
+        <v>40211.35</v>
       </c>
       <c r="I8" t="n">
         <v>40242.0369901602</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.52</v>
+        <v>-5.88</v>
       </c>
       <c r="L8" t="n">
         <v>6.47</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>5.2</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44650.55208333334</v>
+        <v>44651.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>41800</v>
+        <v>43410</v>
       </c>
       <c r="I9" t="n">
         <v>42302.68153755666</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.95</v>
+        <v>-7.95</v>
       </c>
       <c r="L9" t="n">
-        <v>5.07</v>
+        <v>8.02</v>
       </c>
       <c r="M9" t="n">
         <v>0.74</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="O9" t="n">
         <v>-0.71</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.69</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44687.55208333334</v>
+        <v>44690.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>45025</v>
+        <v>42956.1</v>
       </c>
       <c r="I10" t="n">
         <v>43814.90224660787</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K10" t="n">
-        <v>3.72</v>
+        <v>-1.05</v>
       </c>
       <c r="L10" t="n">
         <v>3.71</v>
@@ -1011,7 +1130,7 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>5.47</v>
       </c>
       <c r="O10" t="n">
         <v>3.08</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44707.55208333334</v>
+        <v>44708.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>42495</v>
+        <v>44329.65</v>
       </c>
       <c r="I11" t="n">
         <v>43648.18389448088</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>1.07</v>
+        <v>-3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>5.18</v>
       </c>
       <c r="M11" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="N11" t="n">
-        <v>2.64</v>
+        <v>4.37</v>
       </c>
       <c r="O11" t="n">
         <v>-5.47</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44715.55208333334</v>
+        <v>44718.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>42558.05</v>
+        <v>41905.75</v>
       </c>
       <c r="I12" t="n">
         <v>42045.2165856489</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>-4</v>
+        <v>-5.47</v>
       </c>
       <c r="L12" t="n">
-        <v>4.83</v>
+        <v>5.77</v>
       </c>
       <c r="M12" t="n">
         <v>0.23</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44743.38541666666</v>
+        <v>44743.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>41050.4</v>
+        <v>41236.6</v>
       </c>
       <c r="I13" t="n">
         <v>41134.86826690377</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="L13" t="n">
         <v>2.08</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44817.38541666666</v>
+        <v>44817.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>48751.6</v>
+        <v>48405</v>
       </c>
       <c r="I14" t="n">
         <v>48518.53320258461</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>73.83333333333333</v>
+        <v>74</v>
       </c>
       <c r="K14" t="n">
-        <v>18.22</v>
+        <v>17.38</v>
       </c>
       <c r="L14" t="n">
         <v>0.74</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>4.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44823.55208333334</v>
+        <v>44824.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>48513</v>
+        <v>50400.1</v>
       </c>
       <c r="I15" t="n">
         <v>50147.72599096368</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.22</v>
+        <v>-4.12</v>
       </c>
       <c r="L15" t="n">
-        <v>2.54</v>
+        <v>4.32</v>
       </c>
       <c r="M15" t="n">
         <v>0.64</v>
       </c>
       <c r="N15" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
         <v>-1.72</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44830.55208333334</v>
+        <v>44831.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>50600</v>
+        <v>49872.2</v>
       </c>
       <c r="I16" t="n">
         <v>50084.76021382232</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4</v>
+        <v>-1.05</v>
       </c>
       <c r="L16" t="n">
         <v>3.17</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>52030</v>
+        <v>53500</v>
       </c>
       <c r="I17" t="n">
         <v>52778.16160372466</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.33</v>
+        <v>-7.27</v>
       </c>
       <c r="L17" t="n">
-        <v>5.64</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>1.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44861.55208333334</v>
+        <v>44862.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>51000</v>
+        <v>49442.65</v>
       </c>
       <c r="I18" t="n">
         <v>50889.4788503138</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.67</v>
+        <v>-7.58</v>
       </c>
       <c r="L18" t="n">
-        <v>6.35</v>
+        <v>7.85</v>
       </c>
       <c r="M18" t="n">
         <v>1.93</v>
       </c>
       <c r="N18" t="n">
-        <v>2.57</v>
+        <v>3.41</v>
       </c>
       <c r="O18" t="n">
         <v>1.78</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45005.38541666666</v>
+        <v>45005.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>37450</v>
+        <v>37950</v>
       </c>
       <c r="I19" t="n">
         <v>37697.86240398933</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>143</v>
+        <v>143.1666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>24.26</v>
+        <v>23.24</v>
       </c>
       <c r="L19" t="n">
         <v>4.16</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>195</v>
+        <v>196</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>4.95</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45009.38541666666</v>
+        <v>45009.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>37422</v>
+        <v>37100</v>
       </c>
       <c r="I20" t="n">
         <v>37141.79446073362</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.39</v>
+        <v>-2.24</v>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>2.47</v>
       </c>
       <c r="M20" t="n">
         <v>0.26</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.37</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>37730</v>
+        <v>37993.75</v>
       </c>
       <c r="I21" t="n">
         <v>37926.14912107219</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7</v>
+        <v>-2.41</v>
       </c>
       <c r="L21" t="n">
         <v>4.04</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.39</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45070.38541666666</v>
+        <v>45070.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>41575</v>
+        <v>41090</v>
       </c>
       <c r="I22" t="n">
         <v>41277.26062926415</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>9.43</v>
+        <v>8.15</v>
       </c>
       <c r="L22" t="n">
         <v>0.9</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.63</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>36678.95</v>
+        <v>37518.75</v>
       </c>
       <c r="I23" t="n">
         <v>37106.88913876403</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>58</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>10.74</v>
+        <v>8.69</v>
       </c>
       <c r="L23" t="n">
         <v>1.19</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>39520</v>
+        <v>39140</v>
       </c>
       <c r="I24" t="n">
         <v>39434.19087848573</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>5.33</v>
+        <v>4.32</v>
       </c>
       <c r="L24" t="n">
         <v>2.72</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45174.55208333334</v>
+        <v>45175.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>39518.95</v>
+        <v>40949.55</v>
       </c>
       <c r="I25" t="n">
         <v>40697.05775992921</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.97</v>
+        <v>-4.62</v>
       </c>
       <c r="L25" t="n">
-        <v>3.99</v>
+        <v>5.14</v>
       </c>
       <c r="M25" t="n">
         <v>0.54</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9</v>
+        <v>3.49</v>
       </c>
       <c r="O25" t="n">
         <v>-2.15</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.54</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>40921.55</v>
+        <v>40077.15</v>
       </c>
       <c r="I26" t="n">
         <v>40662.99037121045</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.13</v>
       </c>
       <c r="L26" t="n">
         <v>3.67</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.74</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>37925</v>
+        <v>38449.9</v>
       </c>
       <c r="I27" t="n">
         <v>38280.834472224</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>105.1666666666667</v>
+        <v>106</v>
       </c>
       <c r="K27" t="n">
-        <v>5.37</v>
+        <v>4.06</v>
       </c>
       <c r="L27" t="n">
         <v>3.24</v>
@@ -1980,7 +2303,7 @@
         <v>1.19</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
         <v>-1.76</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.22</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>37720</v>
+        <v>36871.4</v>
       </c>
       <c r="I28" t="n">
         <v>37701.58770228521</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.9</v>
+        <v>-4.11</v>
       </c>
       <c r="L28" t="n">
-        <v>2.31</v>
+        <v>4.4</v>
       </c>
       <c r="M28" t="n">
         <v>0.22</v>
       </c>
       <c r="N28" t="n">
-        <v>3.03</v>
+        <v>3.23</v>
       </c>
       <c r="O28" t="n">
         <v>1.65</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.02</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45357.55208333334</v>
+        <v>45358.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>35740</v>
+        <v>35890</v>
       </c>
       <c r="I29" t="n">
         <v>35845.21240629249</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K29" t="n">
-        <v>3.07</v>
+        <v>2.66</v>
       </c>
       <c r="L29" t="n">
         <v>7.83</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4.53</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>35146</v>
+        <v>34356.25</v>
       </c>
       <c r="I30" t="n">
         <v>34655.91277171244</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.07</v>
+        <v>-4.27</v>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>4.59</v>
       </c>
       <c r="M30" t="n">
         <v>0.22</v>
       </c>
       <c r="N30" t="n">
-        <v>1.96</v>
+        <v>3.69</v>
       </c>
       <c r="O30" t="n">
         <v>0.46</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.68</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45390.55208333334</v>
+        <v>45391.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>35089</v>
+        <v>36340</v>
       </c>
       <c r="I31" t="n">
         <v>35314.67526744949</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.13</v>
+        <v>-5.77</v>
       </c>
       <c r="L31" t="n">
-        <v>4.78</v>
+        <v>6.01</v>
       </c>
       <c r="M31" t="n">
         <v>1.31</v>
       </c>
       <c r="N31" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="O31" t="n">
         <v>-3.69</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>35700</v>
+        <v>35000</v>
       </c>
       <c r="I32" t="n">
         <v>35392.71467032374</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.76</v>
+        <v>-3.69</v>
       </c>
       <c r="L32" t="n">
         <v>3.96</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.31</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>35632.4</v>
+        <v>35809.2</v>
       </c>
       <c r="I33" t="n">
         <v>35709.95205668242</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.81</v>
+        <v>-2.31</v>
       </c>
       <c r="L33" t="n">
         <v>4.11</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.86</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45476.38541666666</v>
+        <v>45476.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>38853</v>
+        <v>38300</v>
       </c>
       <c r="I34" t="n">
         <v>38786.02205964633</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>8.5</v>
+        <v>6.96</v>
       </c>
       <c r="L34" t="n">
         <v>3.59</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.25</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45485.55208333334</v>
+        <v>45488.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>39800</v>
+        <v>40502.45</v>
       </c>
       <c r="I35" t="n">
         <v>40170.81009126201</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.92</v>
+        <v>-5.75</v>
       </c>
       <c r="L35" t="n">
-        <v>4.33</v>
+        <v>6.27</v>
       </c>
       <c r="M35" t="n">
         <v>0.86</v>
       </c>
       <c r="N35" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="O35" t="n">
         <v>-1.82</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.19</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45512.38541666666</v>
+        <v>45512.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>41038.45</v>
+        <v>40301</v>
       </c>
       <c r="I36" t="n">
         <v>40668.3411422021</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>1.32</v>
+        <v>-0.5</v>
       </c>
       <c r="L36" t="n">
         <v>3.38</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45533.55208333334</v>
+        <v>45534.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>41850</v>
+        <v>42718</v>
       </c>
       <c r="I37" t="n">
         <v>42436.14415198143</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.84</v>
+        <v>-6</v>
       </c>
       <c r="L37" t="n">
-        <v>5.36</v>
+        <v>6.2</v>
       </c>
       <c r="M37" t="n">
         <v>1.61</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>41054.4</v>
+        <v>40578.4</v>
       </c>
       <c r="I38" t="n">
         <v>40832.14733634984</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.89</v>
+        <v>-5.01</v>
       </c>
       <c r="L38" t="n">
-        <v>4.14</v>
+        <v>5.39</v>
       </c>
       <c r="M38" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O38" t="n">
         <v>1.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45545.55208333334</v>
+        <v>45546.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>40316.1</v>
+        <v>42467.95</v>
       </c>
       <c r="I39" t="n">
         <v>41818.23508426527</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>0.65</v>
+        <v>-4.66</v>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>4.86</v>
       </c>
       <c r="M39" t="n">
         <v>0.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O39" t="n">
         <v>-1.59</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.13</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>41931.05</v>
+        <v>41382</v>
       </c>
       <c r="I40" t="n">
         <v>41407.85670318914</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.26</v>
+        <v>-2.56</v>
       </c>
       <c r="L40" t="n">
         <v>5.1</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.76</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>42323.8</v>
+        <v>43670.7</v>
       </c>
       <c r="I41" t="n">
         <v>43445.03001904849</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.28</v>
+        <v>-5.53</v>
       </c>
       <c r="L41" t="n">
-        <v>3.82</v>
+        <v>5.97</v>
       </c>
       <c r="M41" t="n">
         <v>1.34</v>
       </c>
       <c r="N41" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0.21</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.93</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>44577.2</v>
+        <v>44192.75</v>
       </c>
       <c r="I42" t="n">
         <v>44270.16166974706</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>2.08</v>
+        <v>1.2</v>
       </c>
       <c r="L42" t="n">
         <v>3.21</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>5.82</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45603.55208333334</v>
+        <v>45604.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>45150</v>
+        <v>48003.95</v>
       </c>
       <c r="I43" t="n">
         <v>45349.13799158238</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.17</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>2.94</v>
+        <v>9.16</v>
       </c>
       <c r="M43" t="n">
         <v>0.87</v>
       </c>
       <c r="N43" t="n">
-        <v>2.02</v>
+        <v>5.92</v>
       </c>
       <c r="O43" t="n">
         <v>-0.74</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.98</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>45296.6</v>
+        <v>44490.85</v>
       </c>
       <c r="I44" t="n">
         <v>44948.78955245228</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.64</v>
+        <v>-7.32</v>
       </c>
       <c r="L44" t="n">
-        <v>6.67</v>
+        <v>7.6</v>
       </c>
       <c r="M44" t="n">
         <v>0.66</v>
       </c>
       <c r="N44" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="O44" t="n">
         <v>5.92</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45636.38541666666</v>
+        <v>45636.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>46641.95</v>
+        <v>46894.6</v>
       </c>
       <c r="I45" t="n">
         <v>46773.35426041616</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.83</v>
+        <v>-5.4</v>
       </c>
       <c r="L45" t="n">
         <v>5.67</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.61</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45650.55208333334</v>
+        <v>45652.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>48779</v>
+        <v>47251.8</v>
       </c>
       <c r="I46" t="n">
         <v>47442.35309517702</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>4.02</v>
+        <v>0.76</v>
       </c>
       <c r="L46" t="n">
         <v>0.79</v>
@@ -3063,7 +3614,7 @@
         <v>0.19</v>
       </c>
       <c r="N46" t="n">
-        <v>0.89</v>
+        <v>3.31</v>
       </c>
       <c r="O46" t="n">
         <v>1.52</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.14</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>47964.75</v>
+        <v>48973.35</v>
       </c>
       <c r="I47" t="n">
         <v>48841.75318648353</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.51</v>
+        <v>-3.64</v>
       </c>
       <c r="L47" t="n">
-        <v>3.65</v>
+        <v>4.24</v>
       </c>
       <c r="M47" t="n">
         <v>0.7</v>
       </c>
       <c r="N47" t="n">
-        <v>1.05</v>
+        <v>1.66</v>
       </c>
       <c r="O47" t="n">
         <v>-3.31</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.05</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45667.38541666666</v>
+        <v>45667.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>46820.05</v>
+        <v>46625</v>
       </c>
       <c r="I48" t="n">
         <v>46645.55246235709</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.4</v>
+        <v>-4.8</v>
       </c>
       <c r="L48" t="n">
-        <v>4.44</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
         <v>0.19</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.34</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>46501</v>
+        <v>47198.75</v>
       </c>
       <c r="I49" t="n">
         <v>46957.49238980887</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>0.27</v>
+        <v>-1.23</v>
       </c>
       <c r="L49" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M49" t="n">
         <v>0.83</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.1</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>45798</v>
+        <v>44023.1</v>
       </c>
       <c r="I50" t="n">
         <v>44103.00741659648</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.97</v>
+        <v>-6.73</v>
       </c>
       <c r="L50" t="n">
-        <v>3.79</v>
+        <v>7.81</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="N50" t="n">
-        <v>2.95</v>
+        <v>4.04</v>
       </c>
       <c r="O50" t="n">
         <v>0.86</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.29</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>41143.3</v>
+        <v>42107</v>
       </c>
       <c r="I51" t="n">
         <v>41551.1014282459</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>6.54</v>
+        <v>4.35</v>
       </c>
       <c r="L51" t="n">
         <v>3.2</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.56</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45743.38541666666</v>
+        <v>45743.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>42150</v>
+        <v>41000</v>
       </c>
       <c r="I52" t="n">
         <v>41462.81248141595</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1</v>
+        <v>-2.63</v>
       </c>
       <c r="L52" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="M52" t="n">
         <v>0.75</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>10.86</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45758.38541666666</v>
+        <v>45758.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>43052.4</v>
+        <v>44440.9</v>
       </c>
       <c r="I53" t="n">
         <v>44169.22613239141</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.01</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>9.15</v>
       </c>
       <c r="M53" t="n">
         <v>6.1</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.25</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>46175</v>
+        <v>45740</v>
       </c>
       <c r="I54" t="n">
         <v>45763.14348538459</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>49</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="L54" t="n">
         <v>3.25</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.3</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>46355</v>
+        <v>47350</v>
       </c>
       <c r="I55" t="n">
         <v>46450.89091623679</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.34</v>
+        <v>-3.52</v>
       </c>
       <c r="L55" t="n">
-        <v>3.82</v>
+        <v>4.24</v>
       </c>
       <c r="M55" t="n">
         <v>1.82</v>
       </c>
       <c r="N55" t="n">
-        <v>1.88</v>
+        <v>4.09</v>
       </c>
       <c r="O55" t="n">
         <v>-0.73</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.03</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45856.38541666666</v>
+        <v>45856.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>47030</v>
+        <v>46600</v>
       </c>
       <c r="I56" t="n">
         <v>46953.9496501316</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.68</v>
+        <v>-1.58</v>
       </c>
       <c r="L56" t="n">
         <v>2.66</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.96</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45867.55208333334</v>
+        <v>45868.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>47215</v>
+        <v>48480</v>
       </c>
       <c r="I57" t="n">
         <v>48200.58346232546</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.32</v>
+        <v>-4.03</v>
       </c>
       <c r="L57" t="n">
-        <v>2.55</v>
+        <v>4.51</v>
       </c>
       <c r="M57" t="n">
         <v>0.65</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="O57" t="n">
         <v>-1.44</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.99</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45873.38541666666</v>
+        <v>45873.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>46565</v>
+        <v>46180</v>
       </c>
       <c r="I58" t="n">
         <v>46553.72048497332</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.95</v>
+        <v>-4.74</v>
       </c>
       <c r="L58" t="n">
-        <v>4.08</v>
+        <v>4.74</v>
       </c>
       <c r="M58" t="n">
         <v>1.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.43</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45889.55208333334</v>
+        <v>45890.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>45600</v>
+        <v>46230</v>
       </c>
       <c r="I59" t="n">
         <v>45768.21093702177</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>1.26</v>
+        <v>-0.11</v>
       </c>
       <c r="L59" t="n">
         <v>1.17</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.3</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>45715</v>
+        <v>43995</v>
       </c>
       <c r="I60" t="n">
         <v>44755.52009631823</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.11</v>
+        <v>-4.83</v>
       </c>
       <c r="L60" t="n">
-        <v>2.18</v>
+        <v>5.16</v>
       </c>
       <c r="M60" t="n">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
       <c r="N60" t="n">
-        <v>2.32</v>
+        <v>3.97</v>
       </c>
       <c r="O60" t="n">
         <v>0.52</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.29</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45916.55208333334</v>
+        <v>45917.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>45460</v>
+        <v>45650</v>
       </c>
       <c r="I61" t="n">
         <v>45619.0427135689</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.33</v>
+        <v>-3.76</v>
       </c>
       <c r="L61" t="n">
-        <v>4.01</v>
+        <v>4.31</v>
       </c>
       <c r="M61" t="n">
         <v>0.85</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>3.76</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45918.55208333334</v>
+        <v>45919.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>44320</v>
+        <v>43625</v>
       </c>
       <c r="I62" t="n">
         <v>43933.9873180647</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.91</v>
+        <v>-4.44</v>
       </c>
       <c r="L62" t="n">
-        <v>3.41</v>
+        <v>4.64</v>
       </c>
       <c r="M62" t="n">
         <v>0.54</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.22</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45933.38541666666</v>
+        <v>45933.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>41915</v>
+        <v>42945</v>
       </c>
       <c r="I63" t="n">
         <v>42505.66994217184</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>3.92</v>
+        <v>1.56</v>
       </c>
       <c r="L63" t="n">
         <v>1.97</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.95</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>40480</v>
+        <v>40370</v>
       </c>
       <c r="I64" t="n">
         <v>40403.55090584695</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.74</v>
+        <v>-6</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="M64" t="n">
         <v>0.33</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.73</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45973.55208333334</v>
+        <v>45974.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>40735</v>
+        <v>41105</v>
       </c>
       <c r="I65" t="n">
         <v>41041.44351054943</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.9</v>
+        <v>-1.82</v>
       </c>
       <c r="L65" t="n">
         <v>4.29</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>4.25</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45974.38541666666</v>
+        <v>45974.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>41105</v>
+        <v>39350</v>
       </c>
       <c r="I66" t="n">
         <v>39356.12473544118</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>-4.27</v>
       </c>
       <c r="L66" t="n">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N66" t="n">
         <v>3.4</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.18</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46057.38541666666</v>
+        <v>46057.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>33865</v>
+        <v>34435</v>
       </c>
       <c r="I67" t="n">
         <v>34077.08184777259</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>82.83333333333333</v>
+        <v>83</v>
       </c>
       <c r="K67" t="n">
-        <v>13.94</v>
+        <v>12.49</v>
       </c>
       <c r="L67" t="n">
         <v>4.78</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.56</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46071.55208333334</v>
+        <v>46072.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>33430</v>
+        <v>32900</v>
       </c>
       <c r="I68" t="n">
         <v>33208.18425775363</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.92</v>
+        <v>-4.46</v>
       </c>
       <c r="L68" t="n">
-        <v>3.5</v>
+        <v>4.57</v>
       </c>
       <c r="M68" t="n">
         <v>2.77</v>
       </c>
       <c r="N68" t="n">
-        <v>2.24</v>
+        <v>2.57</v>
       </c>
       <c r="O68" t="n">
         <v>1.15</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.92</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46099.38541666666</v>
+        <v>46099.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>31605</v>
+        <v>31760</v>
       </c>
       <c r="I69" t="n">
         <v>31657.25619256331</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>3.94</v>
+        <v>3.47</v>
       </c>
       <c r="L69" t="n">
         <v>2.13</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.22</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>36295</v>
+        <v>35425</v>
       </c>
       <c r="I70" t="n">
         <v>36279.01618199048</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>14.28</v>
+        <v>11.54</v>
       </c>
       <c r="L70" t="n">
         <v>2.24</v>
@@ -4431,7 +5270,7 @@
         <v>1.28</v>
       </c>
       <c r="N70" t="n">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="O70" t="n">
         <v>4.05</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.32</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>36870</v>
+        <v>37145</v>
       </c>
       <c r="I71" t="n">
         <v>36976.17292457972</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.08</v>
+        <v>-4.86</v>
       </c>
       <c r="L71" t="n">
-        <v>4.16</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
         <v>0.26</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.61</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46211.55208333334</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>41395</v>
+        <v>40675</v>
       </c>
       <c r="I72" t="n">
         <v>40957.92603666965</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K72" t="n">
-        <v>11.44</v>
+        <v>9.5</v>
       </c>
       <c r="L72" t="n">
         <v>2.52</v>
@@ -4545,7 +5408,7 @@
         <v>1.13</v>
       </c>
       <c r="N72" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="O72" t="n">
         <v>1.82</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.18</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>35600</v>
+        <v>36235</v>
       </c>
       <c r="I73" t="n">
         <v>35825.29962039552</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K73" t="n">
-        <v>12.48</v>
+        <v>10.92</v>
       </c>
       <c r="L73" t="n">
         <v>2.47</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>5.72</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46311.55208333334</v>
+        <v>46314.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>36300</v>
+        <v>35710</v>
       </c>
       <c r="I74" t="n">
         <v>36127.8330663966</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K74" t="n">
-        <v>0.18</v>
+        <v>-1.45</v>
       </c>
       <c r="L74" t="n">
         <v>2.04</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,12 @@
       <c r="Q75" t="n">
         <v>12</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7736,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7756,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7776,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="11">
@@ -6911,7 +7816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.58</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7826,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.86</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7846,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.26</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7856,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7866,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.71</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7876,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.65</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7886,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.220000000000001</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7896,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -7011,7 +7916,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="25">
@@ -7031,7 +7936,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.65</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="27">
@@ -7041,7 +7946,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="28">
@@ -7051,7 +7956,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
